--- a/artfynd/A 41419-2024 artfynd.xlsx
+++ b/artfynd/A 41419-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534495</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534485</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534392</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534391</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534488</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534492</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534493</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534494</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534496</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534526</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534524</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,8 +2074,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534525</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 41419-2024 artfynd.xlsx
+++ b/artfynd/A 41419-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135534495</v>
       </c>
       <c r="B2" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135534487</v>
       </c>
       <c r="B3" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135534485</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135534392</v>
       </c>
       <c r="B5" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135534391</v>
       </c>
       <c r="B6" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>135534488</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>135534492</v>
       </c>
       <c r="B8" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>135534493</v>
       </c>
       <c r="B9" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135534494</v>
       </c>
       <c r="B10" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135534496</v>
       </c>
       <c r="B11" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135534526</v>
       </c>
       <c r="B12" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135534524</v>
       </c>
       <c r="B13" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>135534525</v>
       </c>
       <c r="B14" t="n">
-        <v>99230</v>
+        <v>99277</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 41419-2024 artfynd.xlsx
+++ b/artfynd/A 41419-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135534495</v>
       </c>
       <c r="B2" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135534487</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135534485</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135534392</v>
       </c>
       <c r="B5" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135534391</v>
       </c>
       <c r="B6" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>135534488</v>
       </c>
       <c r="B7" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>135534492</v>
       </c>
       <c r="B8" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>135534493</v>
       </c>
       <c r="B9" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135534494</v>
       </c>
       <c r="B10" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135534496</v>
       </c>
       <c r="B11" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135534526</v>
       </c>
       <c r="B12" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135534524</v>
       </c>
       <c r="B13" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>135534525</v>
       </c>
       <c r="B14" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 41419-2024 artfynd.xlsx
+++ b/artfynd/A 41419-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135534487</v>
       </c>
       <c r="B3" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135534524</v>
       </c>
       <c r="B13" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>135534525</v>
       </c>
       <c r="B14" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 41419-2024 artfynd.xlsx
+++ b/artfynd/A 41419-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135534495</v>
       </c>
       <c r="B2" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135534487</v>
       </c>
       <c r="B3" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135534485</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135534392</v>
       </c>
       <c r="B5" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135534391</v>
       </c>
       <c r="B6" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>135534488</v>
       </c>
       <c r="B7" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>135534492</v>
       </c>
       <c r="B8" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>135534493</v>
       </c>
       <c r="B9" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135534494</v>
       </c>
       <c r="B10" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135534496</v>
       </c>
       <c r="B11" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135534526</v>
       </c>
       <c r="B12" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135534524</v>
       </c>
       <c r="B13" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>135534525</v>
       </c>
       <c r="B14" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 41419-2024 artfynd.xlsx
+++ b/artfynd/A 41419-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135534495</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135534487</v>
       </c>
       <c r="B3" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135534485</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135534392</v>
       </c>
       <c r="B5" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135534391</v>
       </c>
       <c r="B6" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>135534488</v>
       </c>
       <c r="B7" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>135534492</v>
       </c>
       <c r="B8" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>135534493</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>135534494</v>
       </c>
       <c r="B10" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135534496</v>
       </c>
       <c r="B11" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135534526</v>
       </c>
       <c r="B12" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135534524</v>
       </c>
       <c r="B13" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>135534525</v>
       </c>
       <c r="B14" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
